--- a/Excel/AIConfig.xlsx
+++ b/Excel/AIConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="809" activeTab="13"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="842" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="AIConfig_1" sheetId="6" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="58">
   <si>
     <t>cs</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>AI_Turtle</t>
+  </si>
+  <si>
+    <t>#幽灵</t>
+  </si>
+  <si>
+    <t>AI_GhostFollow</t>
+  </si>
+  <si>
+    <t>AI_GhostMove</t>
+  </si>
+  <si>
+    <t>移动</t>
   </si>
 </sst>
 </file>
@@ -850,7 +862,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -860,6 +871,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2621,8 +2633,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="37.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="1" t="s">
@@ -2647,7 +2663,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="3"/>
@@ -2731,7 +2747,7 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="1">
-        <f>D6*100+E6</f>
+        <f t="shared" ref="C6:C8" si="0">D6*100+E6</f>
         <v>1401</v>
       </c>
       <c r="D6" s="1">
@@ -2741,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>24</v>
@@ -2755,23 +2771,21 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="1">
-        <f>D7*100+E7</f>
+        <f t="shared" si="0"/>
         <v>1402</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>14</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+        <v>57</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
@@ -2779,20 +2793,20 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="1">
-        <f>D8*100+E8</f>
+        <f t="shared" si="0"/>
         <v>1403</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>14</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -2802,11 +2816,22 @@
     <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="C9" s="1">
+        <f>D9*100+E9</f>
+        <v>1404</v>
+      </c>
+      <c r="D9" s="1">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -2915,19 +2940,6 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3087,7 +3099,7 @@
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3198,7 +3210,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
@@ -3224,7 +3236,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3305,7 +3317,7 @@
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="3:9">
@@ -3313,7 +3325,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
@@ -3335,7 +3347,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3413,14 +3425,14 @@
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="3:8">
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="3"/>
     </row>
   </sheetData>
@@ -3436,13 +3448,13 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="9" style="6"/>
-    <col min="4" max="4" width="17" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9" style="6"/>
-    <col min="6" max="6" width="20.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="6" customWidth="1"/>
-    <col min="8" max="8" width="30.125" style="6" customWidth="1"/>
-    <col min="9" max="10" width="9" style="6"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="4" width="17" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5"/>
+    <col min="6" max="6" width="20.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="5" customWidth="1"/>
+    <col min="8" max="8" width="30.125" style="5" customWidth="1"/>
+    <col min="9" max="10" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
@@ -3456,7 +3468,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
-      <c r="I1" s="5"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" ht="16.5" spans="1:9">
       <c r="A2" s="1"/>
@@ -3469,7 +3481,7 @@
         <v>33</v>
       </c>
       <c r="H2" s="8"/>
-      <c r="I2" s="5"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" ht="16.5" spans="1:9">
       <c r="A3" s="1"/>
@@ -3490,7 +3502,7 @@
       <c r="H3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" ht="16.5" spans="1:9">
       <c r="A4" s="1"/>
@@ -3513,7 +3525,7 @@
       <c r="H4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="1"/>
@@ -3536,7 +3548,7 @@
       <c r="H5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="3"/>
@@ -3556,8 +3568,8 @@
       <c r="G6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="3"/>
@@ -3577,8 +3589,8 @@
       <c r="G7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="3"/>
@@ -3598,8 +3610,8 @@
       <c r="G8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="3"/>
@@ -3619,8 +3631,8 @@
       <c r="G9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="3"/>
@@ -3640,10 +3652,10 @@
       <c r="G10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3663,7 +3675,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3741,14 +3753,14 @@
       <c r="G6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="3:8">
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="3"/>
     </row>
   </sheetData>
@@ -3770,7 +3782,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3888,7 +3900,7 @@
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="3"/>
@@ -4124,11 +4136,11 @@
       <c r="G7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>1</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="6"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/AIConfig.xlsx
+++ b/Excel/AIConfig.xlsx
@@ -226,7 +226,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,13 +245,6 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -724,136 +717,136 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -861,17 +854,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2747,7 +2740,6 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="1">
-        <f t="shared" ref="C6:C8" si="0">D6*100+E6</f>
         <v>1401</v>
       </c>
       <c r="D6" s="1">
@@ -2771,7 +2763,6 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="1">
-        <f t="shared" si="0"/>
         <v>1402</v>
       </c>
       <c r="D7" s="1">
@@ -2793,7 +2784,6 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="1">
-        <f t="shared" si="0"/>
         <v>1403</v>
       </c>
       <c r="D8" s="1">
@@ -2817,7 +2807,6 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="1">
-        <f>D9*100+E9</f>
         <v>1404</v>
       </c>
       <c r="D9" s="1">
@@ -2836,19 +2825,6 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="3"/>

--- a/Excel/AIConfig.xlsx
+++ b/Excel/AIConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="842" activeTab="13"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="842" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="AIConfig_1" sheetId="6" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="AIConfig_12" sheetId="17" r:id="rId12"/>
     <sheet name="AIConfig_13" sheetId="18" r:id="rId13"/>
     <sheet name="AIConfig_14" sheetId="19" r:id="rId14"/>
+    <sheet name="AIConfig_15" sheetId="20" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="61">
   <si>
     <t>cs</t>
   </si>
@@ -214,6 +215,15 @@
   </si>
   <si>
     <t>移动</t>
+  </si>
+  <si>
+    <t>#宠物+召唤怪  连击</t>
+  </si>
+  <si>
+    <t>AI_Combo</t>
+  </si>
+  <si>
+    <t>连击</t>
   </si>
 </sst>
 </file>
@@ -855,6 +865,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,7 +875,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2923,6 +2933,300 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="6" max="6" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:9">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:9">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:9">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:9">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1">
+        <f>D6*100+E6</f>
+        <v>201</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
+        <v>202</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3">
+        <v>203</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -3075,7 +3379,7 @@
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3186,7 +3490,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
@@ -3212,7 +3516,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3293,7 +3597,7 @@
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="3:9">
@@ -3301,7 +3605,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
@@ -3323,7 +3627,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3401,14 +3705,14 @@
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="3:8">
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="3"/>
     </row>
   </sheetData>
@@ -3424,13 +3728,13 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="9" style="5"/>
-    <col min="4" max="4" width="17" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9" style="5"/>
-    <col min="6" max="6" width="20.875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="5" customWidth="1"/>
-    <col min="8" max="8" width="30.125" style="5" customWidth="1"/>
-    <col min="9" max="10" width="9" style="5"/>
+    <col min="3" max="3" width="9" style="6"/>
+    <col min="4" max="4" width="17" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9" style="6"/>
+    <col min="6" max="6" width="20.875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="6" customWidth="1"/>
+    <col min="8" max="8" width="30.125" style="6" customWidth="1"/>
+    <col min="9" max="10" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
@@ -3444,7 +3748,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
-      <c r="I1" s="4"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" ht="16.5" spans="1:9">
       <c r="A2" s="1"/>
@@ -3457,7 +3761,7 @@
         <v>33</v>
       </c>
       <c r="H2" s="8"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:9">
       <c r="A3" s="1"/>
@@ -3478,7 +3782,7 @@
       <c r="H3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" ht="16.5" spans="1:9">
       <c r="A4" s="1"/>
@@ -3501,7 +3805,7 @@
       <c r="H4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="1"/>
@@ -3524,7 +3828,7 @@
       <c r="H5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="3"/>
@@ -3544,8 +3848,8 @@
       <c r="G6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="3"/>
@@ -3565,8 +3869,8 @@
       <c r="G7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="3"/>
@@ -3586,8 +3890,8 @@
       <c r="G8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="3"/>
@@ -3607,8 +3911,8 @@
       <c r="G9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="3"/>
@@ -3628,10 +3932,10 @@
       <c r="G10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <v>1</v>
       </c>
-      <c r="I10" s="4"/>
+      <c r="I10" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3651,7 +3955,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3729,14 +4033,14 @@
       <c r="G6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="3:8">
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="3"/>
     </row>
   </sheetData>
@@ -3758,7 +4062,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:7">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3876,7 +4180,7 @@
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="3"/>
@@ -4112,11 +4416,11 @@
       <c r="G7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <v>1</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/AIConfig.xlsx
+++ b/Excel/AIConfig.xlsx
@@ -3041,10 +3041,10 @@
       <c r="B6" s="3"/>
       <c r="C6" s="1">
         <f>D6*100+E6</f>
-        <v>201</v>
+        <v>1501</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3058,14 +3058,15 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="3">
-        <v>202</v>
+      <c r="C7" s="1">
+        <f>D7*100+E7</f>
+        <v>1502</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
@@ -3079,14 +3080,15 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="3">
-        <v>203</v>
+      <c r="C8" s="1">
+        <f>D8*100+E8</f>
+        <v>1503</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3">
         <v>3</v>

--- a/Excel/AIConfig.xlsx
+++ b/Excel/AIConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="842" activeTab="14"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="842"/>
   </bookViews>
   <sheets>
     <sheet name="AIConfig_1" sheetId="6" r:id="rId1"/>
